--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486673_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486673_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8736</v>
+        <v>0.5675</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9068</v>
+        <v>2.6999</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.0331</v>
+        <v>-2.1324</v>
       </c>
       <c r="G2" t="n">
         <v>0.5778</v>
@@ -610,13 +610,13 @@
         <v>1.3515</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0936</v>
+        <v>-0.3998</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3857</v>
+        <v>0.1788</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4793</v>
+        <v>-0.5786</v>
       </c>
       <c r="V2" t="n">
         <v>2.1271</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. FLORES LUCAS</t>
+          <t>P. GRIMA LORENZO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0443</v>
+        <v>0.3603</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4612</v>
+        <v>2.0718</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4168</v>
+        <v>-1.7115</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4354</v>
+        <v>1.7531</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0619</v>
+        <v>0.4487</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4974</v>
+        <v>1.3043</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1028</v>
+        <v>4.4718</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0621</v>
+        <v>2.5186</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0407</v>
+        <v>1.9532</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5382</v>
+        <v>-2.7187</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0002</v>
+        <v>-2.0698</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5381</v>
+        <v>-0.6489</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1931</v>
+        <v>-2.8962</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1931</v>
+        <v>1.5446</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4798</v>
+        <v>-0.6551</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5515</v>
+        <v>-0.1177</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0717</v>
+        <v>-0.5374</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. GRIMA LORENZO</t>
+          <t>L. FLORES LUCAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0279</v>
+        <v>-0.1666</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9132</v>
+        <v>0.1509</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8854</v>
+        <v>-0.3175</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7531</v>
+        <v>-0.4354</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4487</v>
+        <v>0.0619</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3043</v>
+        <v>-0.4974</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4718</v>
+        <v>0.1028</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5186</v>
+        <v>0.0621</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9532</v>
+        <v>0.0407</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.7187</v>
+        <v>-0.5382</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.0698</v>
+        <v>-0.0002</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6489</v>
+        <v>-0.5381</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.3515</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.8962</v>
+        <v>-0.1931</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5446</v>
+        <v>0.1931</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9875</v>
+        <v>0.2688</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2763</v>
+        <v>0.2412</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7113</v>
+        <v>0.0277</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PARRONDO CASTRO</t>
+          <t>M. DIAZ FELST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3453</v>
+        <v>-0.5733</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5776</v>
+        <v>-0.0835</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9228</v>
+        <v>-0.4898</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6132</v>
+        <v>-0.394</v>
       </c>
       <c r="H5" t="n">
-        <v>1.001</v>
+        <v>-0.4415</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6142</v>
+        <v>0.0475</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1612</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>2.7263</v>
+        <v>0.0414</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5651</v>
+        <v>0.0407</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.7744</v>
+        <v>-0.4761</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7253</v>
+        <v>-0.4829</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.049</v>
+        <v>0.0068</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.7377</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.0892</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3515</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7779</v>
+        <v>-0.1793</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9923</v>
+        <v>-0.1655</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2144</v>
+        <v>-0.0137</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. DIAZ FELST</t>
+          <t>J. MORENO CASTRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6478</v>
+        <v>-0.7981</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0835</v>
+        <v>0.3885</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5643</v>
+        <v>-1.1866</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.394</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4415</v>
+        <v>0.855</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0475</v>
+        <v>-0.1085</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08210000000000001</v>
+        <v>1.685</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0414</v>
+        <v>0.9932</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0407</v>
+        <v>0.6918</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4761</v>
+        <v>-0.9385</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4829</v>
+        <v>-0.1382</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0068</v>
+        <v>-0.8003</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.1931</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2538</v>
+        <v>-0.7723</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1655</v>
+        <v>-0.3311</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0882</v>
+        <v>-0.4412</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MORENO CASTRO</t>
+          <t>D. FLORES LUCAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.9603</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3885</v>
+        <v>-1.8561</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3356</v>
+        <v>0.8958</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7465000000000001</v>
+        <v>-1.6638</v>
       </c>
       <c r="H7" t="n">
-        <v>0.855</v>
+        <v>-2.4482</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1085</v>
+        <v>0.7844</v>
       </c>
       <c r="J7" t="n">
-        <v>1.685</v>
+        <v>-1.4697</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9932</v>
+        <v>-1.5511</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6918</v>
+        <v>0.0814</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9385</v>
+        <v>-0.194</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1382</v>
+        <v>-0.897</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8003</v>
+        <v>0.703</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7723</v>
+        <v>0.7723</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9654</v>
+        <v>-0.1931</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9212</v>
+        <v>-0.0689</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3311</v>
+        <v>-0.1933</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5901999999999999</v>
+        <v>0.1245</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. FLORES LUCAS</t>
+          <t>J. PARRONDO CASTRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2002</v>
+        <v>-1.3369</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2698</v>
+        <v>0.9088000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0697</v>
+        <v>-2.2456</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6638</v>
+        <v>-0.6132</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.4482</v>
+        <v>1.001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7844</v>
+        <v>-1.6142</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.4697</v>
+        <v>2.1612</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.5511</v>
+        <v>2.7263</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0814</v>
+        <v>-0.5651</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.194</v>
+        <v>-2.7744</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.897</v>
+        <v>-1.7253</v>
       </c>
       <c r="O8" t="n">
-        <v>0.703</v>
+        <v>-1.049</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7723</v>
+        <v>-1.7377</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1931</v>
+        <v>-3.0892</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3087</v>
+        <v>-0.2136</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.607</v>
+        <v>0.3236</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2983</v>
+        <v>-0.5372</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4961</v>
+        <v>-1.4216</v>
       </c>
       <c r="E9" t="n">
         <v>-0.118</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3782</v>
+        <v>-1.3037</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9114</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5848</v>
+        <v>-0.5103</v>
       </c>
       <c r="T9" t="n">
         <v>-0.2207</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.364</v>
+        <v>-0.2895</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0334</v>
+        <v>-2.8914</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4563</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5771</v>
+        <v>-2.8006</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5189</v>
@@ -1234,13 +1234,13 @@
         <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.531</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5243</v>
+        <v>-0.1588</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1486</v>
+        <v>-0.3721</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6138</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3114</v>
+        <v>-3.6699</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3148</v>
+        <v>-2.6733</v>
       </c>
       <c r="F11" t="n">
         <v>-0.9966</v>
@@ -1312,10 +1312,10 @@
         <v>0.7723</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2206</v>
+        <v>-0.1379</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2204</v>
+        <v>-0.1381</v>
       </c>
       <c r="U11" t="n">
         <v>0.0002</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.8608</v>
+        <v>-5.7299</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.5145</v>
+        <v>-4.632</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3462</v>
+        <v>-1.0979</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2476</v>
@@ -1390,13 +1390,13 @@
         <v>1.5446</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.0686</v>
+        <v>-0.9377</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9933</v>
+        <v>-0.1107</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0753</v>
+        <v>-0.827</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.8963</v>
+        <v>-16.6202</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.509599999999999</v>
+        <v>-3.233799999999999</v>
       </c>
       <c r="F13" t="n">
         <v>-13.3864</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.794799999999999</v>
+        <v>-8.7948</v>
       </c>
       <c r="H13" t="n">
         <v>-2.7588</v>
@@ -1441,7 +1441,7 @@
         <v>-6.0361</v>
       </c>
       <c r="J13" t="n">
-        <v>7.423099999999998</v>
+        <v>7.4231</v>
       </c>
       <c r="K13" t="n">
         <v>6.213200000000001</v>
@@ -1453,7 +1453,7 @@
         <v>-16.2179</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.971800000000002</v>
+        <v>-8.9718</v>
       </c>
       <c r="O13" t="n">
         <v>-7.245900000000001</v>
@@ -1468,13 +1468,13 @@
         <v>8.688399999999998</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.4128</v>
+        <v>-4.1371</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9682999999999999</v>
+        <v>-0.6923</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.4445</v>
+        <v>-3.4443</v>
       </c>
       <c r="V13" t="n">
         <v>3.0692</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.9257</v>
+        <v>12.0913</v>
       </c>
       <c r="E14" t="n">
-        <v>11.3549</v>
+        <v>10.631</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5708</v>
+        <v>1.4603</v>
       </c>
       <c r="G14" t="n">
         <v>6.1896</v>
@@ -1546,13 +1546,13 @@
         <v>3.0892</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2341</v>
+        <v>1.3997</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6542</v>
+        <v>0.9302</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5799</v>
+        <v>0.4695</v>
       </c>
       <c r="V14" t="n">
         <v>1.7989</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.2547</v>
+        <v>6.1373</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8036</v>
+        <v>4.4242</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4511</v>
+        <v>1.7132</v>
       </c>
       <c r="G15" t="n">
         <v>5.5404</v>
@@ -1624,13 +1624,13 @@
         <v>2.1239</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0001</v>
+        <v>0.8825</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1384</v>
+        <v>0.4822</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1383</v>
+        <v>0.4004</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2856</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3928</v>
+        <v>4.0163</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5135</v>
+        <v>3.4101</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8793</v>
+        <v>0.6062</v>
       </c>
       <c r="G16" t="n">
         <v>2.2579</v>
@@ -1702,13 +1702,13 @@
         <v>1.7377</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5903</v>
+        <v>0.2138</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2204</v>
+        <v>0.117</v>
       </c>
       <c r="U16" t="n">
-        <v>0.37</v>
+        <v>0.0968</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4124</v>
+        <v>2.2359</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2715</v>
+        <v>2.8578</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8591</v>
+        <v>-0.6219</v>
       </c>
       <c r="G17" t="n">
         <v>1.5675</v>
@@ -1780,13 +1780,13 @@
         <v>1.9308</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9487</v>
+        <v>0.7722</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8822</v>
+        <v>0.4685</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0665</v>
+        <v>0.3037</v>
       </c>
       <c r="V17" t="n">
         <v>-1.8415</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.993</v>
+        <v>1.3792</v>
       </c>
       <c r="E18" t="n">
         <v>-0.3204</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3133</v>
+        <v>1.6996</v>
       </c>
       <c r="G18" t="n">
         <v>1.4993</v>
@@ -1858,13 +1858,13 @@
         <v>2.1239</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0277</v>
+        <v>0.3586</v>
       </c>
       <c r="T18" t="n">
         <v>0.1652</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1928</v>
+        <v>0.1934</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2856</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7689</v>
+        <v>0.7786</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8065</v>
+        <v>-0.9099</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5754</v>
+        <v>1.6885</v>
       </c>
       <c r="G19" t="n">
         <v>-1.5039</v>
@@ -1936,13 +1936,13 @@
         <v>1.9308</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7282</v>
+        <v>0.7379</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5512</v>
+        <v>0.4478</v>
       </c>
       <c r="U19" t="n">
-        <v>0.177</v>
+        <v>0.2901</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3502</v>
+        <v>-3.5281</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.81</v>
+        <v>-1.9134</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5402</v>
+        <v>-1.6147</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7899</v>
@@ -2014,13 +2014,13 @@
         <v>1.1585</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0535</v>
+        <v>0.8756</v>
       </c>
       <c r="T20" t="n">
-        <v>0.827</v>
+        <v>0.7236</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2265</v>
+        <v>0.152</v>
       </c>
       <c r="V20" t="n">
         <v>-1.8415</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.5012</v>
+        <v>-5.5248</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.6202</v>
+        <v>-4.7929</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.881</v>
+        <v>-0.732</v>
       </c>
       <c r="G21" t="n">
         <v>-4.9661</v>
@@ -2092,13 +2092,13 @@
         <v>1.3515</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1143</v>
+        <v>-0.138</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7174</v>
+        <v>0.11</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.397</v>
+        <v>-0.248</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6138</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>16.8961</v>
+        <v>17.5857</v>
       </c>
       <c r="E22" t="n">
-        <v>13.3864</v>
+        <v>13.3865</v>
       </c>
       <c r="F22" t="n">
-        <v>3.5096</v>
+        <v>4.199199999999999</v>
       </c>
       <c r="G22" t="n">
         <v>8.7948</v>
@@ -2170,13 +2170,13 @@
         <v>15.4463</v>
       </c>
       <c r="S22" t="n">
-        <v>4.4127</v>
+        <v>5.102300000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>3.4444</v>
+        <v>3.4445</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9684</v>
+        <v>1.6579</v>
       </c>
       <c r="V22" t="n">
         <v>-3.0691</v>
